--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_MONBUS - CB IGUALADA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_MONBUS - CB IGUALADA.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. CUMELLES CESPEDES</t>
+          <t>L. SALA MAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>34.8197</v>
+        <v>23.2751</v>
       </c>
       <c r="E2" t="n">
-        <v>17.744</v>
+        <v>10.9567</v>
       </c>
       <c r="F2" t="n">
-        <v>17.0755</v>
+        <v>12.3184</v>
       </c>
       <c r="G2" t="n">
-        <v>-7.777700000000001</v>
+        <v>-1.082499999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>0.006900000000000572</v>
+        <v>-7.8015</v>
       </c>
       <c r="I2" t="n">
-        <v>-7.7849</v>
+        <v>6.718800000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>14.0534</v>
+        <v>22.7324</v>
       </c>
       <c r="K2" t="n">
-        <v>8.7684</v>
+        <v>6.7198</v>
       </c>
       <c r="L2" t="n">
-        <v>5.2847</v>
+        <v>16.0121</v>
       </c>
       <c r="M2" t="n">
-        <v>-21.8313</v>
+        <v>-23.8149</v>
       </c>
       <c r="N2" t="n">
-        <v>-8.7614</v>
+        <v>-14.521</v>
       </c>
       <c r="O2" t="n">
-        <v>-13.07</v>
+        <v>-9.293799999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.3808</v>
+        <v>23.6077</v>
       </c>
       <c r="Q2" t="n">
-        <v>-52.1747</v>
+        <v>-23.4092</v>
       </c>
       <c r="R2" t="n">
-        <v>49.7941</v>
+        <v>47.017</v>
       </c>
       <c r="S2" t="n">
-        <v>21.8257</v>
+        <v>4.2836</v>
       </c>
       <c r="T2" t="n">
-        <v>14.1959</v>
+        <v>0.6709000000000002</v>
       </c>
       <c r="U2" t="n">
-        <v>7.6295</v>
+        <v>3.6124</v>
       </c>
       <c r="V2" t="n">
-        <v>23.1527</v>
+        <v>-3.5336</v>
       </c>
       <c r="W2" t="n">
-        <v>41.6697</v>
+        <v>10.9626</v>
       </c>
       <c r="X2" t="n">
-        <v>-18.5173</v>
+        <v>-14.4963</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. SALA MAS</t>
+          <t>A. CUMELLES CESPEDES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>21.7809</v>
+        <v>22.9159</v>
       </c>
       <c r="E3" t="n">
-        <v>9.046600000000002</v>
+        <v>9.0488</v>
       </c>
       <c r="F3" t="n">
-        <v>12.7341</v>
+        <v>13.867</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.082499999999999</v>
+        <v>-7.777700000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>-7.8015</v>
+        <v>0.006900000000000572</v>
       </c>
       <c r="I3" t="n">
-        <v>6.718800000000001</v>
+        <v>-7.7849</v>
       </c>
       <c r="J3" t="n">
-        <v>22.7324</v>
+        <v>14.0534</v>
       </c>
       <c r="K3" t="n">
-        <v>6.7198</v>
+        <v>8.7684</v>
       </c>
       <c r="L3" t="n">
-        <v>16.0121</v>
+        <v>5.2847</v>
       </c>
       <c r="M3" t="n">
-        <v>-23.8149</v>
+        <v>-21.8313</v>
       </c>
       <c r="N3" t="n">
-        <v>-14.521</v>
+        <v>-8.7614</v>
       </c>
       <c r="O3" t="n">
-        <v>-9.293799999999999</v>
+        <v>-13.07</v>
       </c>
       <c r="P3" t="n">
-        <v>23.6077</v>
+        <v>-2.3808</v>
       </c>
       <c r="Q3" t="n">
-        <v>-23.4092</v>
+        <v>-52.1747</v>
       </c>
       <c r="R3" t="n">
-        <v>47.017</v>
+        <v>49.7941</v>
       </c>
       <c r="S3" t="n">
-        <v>2.7891</v>
+        <v>9.921899999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.2389</v>
+        <v>5.5007</v>
       </c>
       <c r="U3" t="n">
-        <v>4.0281</v>
+        <v>4.4211</v>
       </c>
       <c r="V3" t="n">
-        <v>-3.5336</v>
+        <v>23.1527</v>
       </c>
       <c r="W3" t="n">
-        <v>10.9626</v>
+        <v>41.6697</v>
       </c>
       <c r="X3" t="n">
-        <v>-14.4963</v>
+        <v>-18.5173</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>18.533</v>
+        <v>14.0607</v>
       </c>
       <c r="E4" t="n">
-        <v>14.6303</v>
+        <v>14.3636</v>
       </c>
       <c r="F4" t="n">
-        <v>3.9025</v>
+        <v>-0.3029999999999997</v>
       </c>
       <c r="G4" t="n">
         <v>-4.1316</v>
@@ -766,13 +766,13 @@
         <v>43.446</v>
       </c>
       <c r="S4" t="n">
-        <v>9.3879</v>
+        <v>4.9158</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2244</v>
+        <v>1.958</v>
       </c>
       <c r="U4" t="n">
-        <v>7.163600000000001</v>
+        <v>2.9579</v>
       </c>
       <c r="V4" t="n">
         <v>0.1832000000000001</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. BALTÀ CASTELLTORT</t>
+          <t>M. BENITO MULLERAT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>18.422</v>
+        <v>13.9417</v>
       </c>
       <c r="E5" t="n">
-        <v>19.5539</v>
+        <v>9.187399999999998</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1316</v>
+        <v>4.7545</v>
       </c>
       <c r="G5" t="n">
-        <v>6.0856</v>
+        <v>26.3134</v>
       </c>
       <c r="H5" t="n">
-        <v>10.6049</v>
+        <v>13.8363</v>
       </c>
       <c r="I5" t="n">
-        <v>-4.5192</v>
+        <v>12.4769</v>
       </c>
       <c r="J5" t="n">
-        <v>19.9433</v>
+        <v>58.9892</v>
       </c>
       <c r="K5" t="n">
-        <v>19.0417</v>
+        <v>31.143</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9010999999999999</v>
+        <v>27.8461</v>
       </c>
       <c r="M5" t="n">
-        <v>-13.8577</v>
+        <v>-32.6757</v>
       </c>
       <c r="N5" t="n">
-        <v>-8.436999999999999</v>
+        <v>-17.3067</v>
       </c>
       <c r="O5" t="n">
-        <v>-5.4207</v>
+        <v>-15.369</v>
       </c>
       <c r="P5" t="n">
-        <v>6.5468</v>
+        <v>4.9596</v>
       </c>
       <c r="Q5" t="n">
-        <v>-20.235</v>
+        <v>-50.3891</v>
       </c>
       <c r="R5" t="n">
-        <v>26.7821</v>
+        <v>55.3492</v>
       </c>
       <c r="S5" t="n">
-        <v>20.9761</v>
+        <v>-2.2429</v>
       </c>
       <c r="T5" t="n">
-        <v>16.7967</v>
+        <v>-2.5138</v>
       </c>
       <c r="U5" t="n">
-        <v>4.1796</v>
+        <v>0.2708999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>-15.186</v>
+        <v>-15.0885</v>
       </c>
       <c r="W5" t="n">
-        <v>3.049300000000001</v>
+        <v>3.1016</v>
       </c>
       <c r="X5" t="n">
-        <v>-18.2352</v>
+        <v>-18.1897</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. ALIAGA CHECA</t>
+          <t>A. BALTÀ CASTELLTORT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
-        <v>10.9794</v>
+        <v>7.148399999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7746</v>
+        <v>9.872300000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>7.205</v>
+        <v>-2.7238</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2614</v>
+        <v>6.0856</v>
       </c>
       <c r="H6" t="n">
-        <v>9.238</v>
+        <v>10.6049</v>
       </c>
       <c r="I6" t="n">
-        <v>-7.9772</v>
+        <v>-4.5192</v>
       </c>
       <c r="J6" t="n">
-        <v>21.3591</v>
+        <v>19.9433</v>
       </c>
       <c r="K6" t="n">
-        <v>22.834</v>
+        <v>19.0417</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.475</v>
+        <v>0.9010999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-20.0977</v>
+        <v>-13.8577</v>
       </c>
       <c r="N6" t="n">
-        <v>-13.596</v>
+        <v>-8.436999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-6.502</v>
+        <v>-5.4207</v>
       </c>
       <c r="P6" t="n">
-        <v>-6.3485</v>
+        <v>6.5468</v>
       </c>
       <c r="Q6" t="n">
-        <v>-47.0166</v>
+        <v>-20.235</v>
       </c>
       <c r="R6" t="n">
-        <v>40.6689</v>
+        <v>26.7821</v>
       </c>
       <c r="S6" t="n">
-        <v>9.9649</v>
+        <v>9.702500000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>13.345</v>
+        <v>7.1153</v>
       </c>
       <c r="U6" t="n">
-        <v>-3.3799</v>
+        <v>2.5875</v>
       </c>
       <c r="V6" t="n">
-        <v>6.101599999999999</v>
+        <v>-15.186</v>
       </c>
       <c r="W6" t="n">
-        <v>16.0874</v>
+        <v>3.049300000000001</v>
       </c>
       <c r="X6" t="n">
-        <v>-9.985900000000001</v>
+        <v>-18.2352</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. RIERA PERETO</t>
+          <t>M. ALIAGA CHECA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6788</v>
+        <v>5.271199999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5418</v>
+        <v>-4.1442</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1371</v>
+        <v>9.4154</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6519</v>
+        <v>1.2614</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1012</v>
+        <v>9.238</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5507</v>
+        <v>-7.9772</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2324</v>
+        <v>21.3591</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2324</v>
+        <v>22.834</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-1.475</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4195</v>
+        <v>-20.0977</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1311</v>
+        <v>-13.596</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5507</v>
+        <v>-6.502</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1984</v>
+        <v>-6.3485</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-47.0166</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1984</v>
+        <v>40.6689</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0945</v>
+        <v>4.2569</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3094</v>
+        <v>5.4265</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2149</v>
+        <v>-1.1696</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.266</v>
+        <v>6.101599999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>16.0874</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.266</v>
+        <v>-9.985900000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MARBÀ RECASENS</t>
+          <t>C. FONS TEIXIDO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9068000000000004</v>
+        <v>3.299599999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6828</v>
+        <v>4.087400000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7761000000000002</v>
+        <v>-0.7876000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1965</v>
+        <v>-8.617999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6759999999999999</v>
+        <v>-7.212599999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5207999999999998</v>
+        <v>-1.4056</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8856</v>
+        <v>20.5351</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9206</v>
+        <v>8.754099999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.03509999999999991</v>
+        <v>11.7807</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.0823</v>
+        <v>-29.1529</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.5965</v>
+        <v>-15.9666</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4857999999999998</v>
+        <v>-13.1867</v>
       </c>
       <c r="P8" t="n">
-        <v>2.7775</v>
+        <v>14.6806</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9838</v>
+        <v>-32.3363</v>
       </c>
       <c r="R8" t="n">
-        <v>4.7614</v>
+        <v>47.0173</v>
       </c>
       <c r="S8" t="n">
-        <v>0.05010000000000003</v>
+        <v>-0.6430999999999998</v>
       </c>
       <c r="T8" t="n">
-        <v>0.38</v>
+        <v>-2.9677</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3300999999999999</v>
+        <v>2.3248</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.7238</v>
+        <v>-2.1194</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4012</v>
+        <v>18.8569</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.125</v>
+        <v>-20.9759</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. VILADRICH SENSERRICH</t>
+          <t>O. RIERA PERETO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,43 +1108,43 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0.548</v>
+        <v>1.161</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0402</v>
+        <v>0.8276</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5079</v>
+        <v>0.3335</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4483</v>
+        <v>0.6519</v>
       </c>
       <c r="H9" t="n">
+        <v>0.1012</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.5507</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.2324</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2324</v>
+      </c>
+      <c r="L9" t="n">
         <v>0</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.4483</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.0402</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.0402</v>
-      </c>
       <c r="M9" t="n">
-        <v>0.4081</v>
+        <v>0.4195</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-0.1311</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4081</v>
+        <v>0.5507</v>
       </c>
       <c r="P9" t="n">
         <v>0.1984</v>
@@ -1156,28 +1156,28 @@
         <v>0.1984</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.09859999999999999</v>
+        <v>0.5767</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.5952000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.0185</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. MARIMON SOTERAS</t>
+          <t>J. MARBÀ RECASENS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.829</v>
+        <v>0.7688999999999998</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5071</v>
+        <v>1.6658</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6780999999999999</v>
+        <v>-0.8967999999999998</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1136</v>
+        <v>-1.1965</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1613</v>
+        <v>-0.6759999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9523</v>
+        <v>-0.5207999999999998</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3201</v>
+        <v>1.8856</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0403</v>
+        <v>1.9206</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3604</v>
+        <v>-0.03509999999999991</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2065</v>
+        <v>-3.0823</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2016</v>
+        <v>-2.5965</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4081</v>
+        <v>-0.4857999999999998</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1984</v>
+        <v>2.7775</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1984</v>
+        <v>-1.9838</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3968</v>
+        <v>4.7614</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0862</v>
+        <v>-0.08779999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0114</v>
+        <v>0.3629000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.07480000000000001</v>
+        <v>-0.4508000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.7238</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.4012</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-2.125</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. BENITO MULLERAT</t>
+          <t>O. VILADRICH SENSERRICH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9283</v>
+        <v>0.6041</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3637000000000001</v>
+        <v>0.0402</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.564799999999999</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>26.3134</v>
+        <v>0.4483</v>
       </c>
       <c r="H11" t="n">
-        <v>13.8363</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>12.4769</v>
+        <v>0.4483</v>
       </c>
       <c r="J11" t="n">
-        <v>58.9892</v>
+        <v>0.0402</v>
       </c>
       <c r="K11" t="n">
-        <v>31.143</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>27.8461</v>
+        <v>0.0402</v>
       </c>
       <c r="M11" t="n">
-        <v>-32.6757</v>
+        <v>0.4081</v>
       </c>
       <c r="N11" t="n">
-        <v>-17.3067</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-15.369</v>
+        <v>0.4081</v>
       </c>
       <c r="P11" t="n">
-        <v>4.9596</v>
+        <v>0.1984</v>
       </c>
       <c r="Q11" t="n">
-        <v>-50.3891</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>55.3492</v>
+        <v>0.1984</v>
       </c>
       <c r="S11" t="n">
-        <v>-19.1133</v>
+        <v>-0.0425</v>
       </c>
       <c r="T11" t="n">
-        <v>-12.0647</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-7.0484</v>
+        <v>-0.0425</v>
       </c>
       <c r="V11" t="n">
-        <v>-15.0885</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.1016</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-18.1897</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C. FONS TEIXIDO</t>
+          <t>R. MARIMON SOTERAS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.741100000000001</v>
+        <v>-0.4107</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3372</v>
+        <v>-1.201</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.403799999999999</v>
+        <v>0.7903</v>
       </c>
       <c r="G12" t="n">
-        <v>-8.617999999999999</v>
+        <v>-1.1136</v>
       </c>
       <c r="H12" t="n">
-        <v>-7.212599999999999</v>
+        <v>-0.1613</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.4056</v>
+        <v>-0.9523</v>
       </c>
       <c r="J12" t="n">
-        <v>20.5351</v>
+        <v>-1.3201</v>
       </c>
       <c r="K12" t="n">
-        <v>8.754099999999999</v>
+        <v>0.0403</v>
       </c>
       <c r="L12" t="n">
-        <v>11.7807</v>
+        <v>-1.3604</v>
       </c>
       <c r="M12" t="n">
-        <v>-29.1529</v>
+        <v>0.2065</v>
       </c>
       <c r="N12" t="n">
-        <v>-15.9666</v>
+        <v>-0.2016</v>
       </c>
       <c r="O12" t="n">
-        <v>-13.1867</v>
+        <v>0.4081</v>
       </c>
       <c r="P12" t="n">
-        <v>14.6806</v>
+        <v>0.1984</v>
       </c>
       <c r="Q12" t="n">
-        <v>-32.3363</v>
+        <v>-0.1984</v>
       </c>
       <c r="R12" t="n">
-        <v>47.0173</v>
+        <v>0.3968</v>
       </c>
       <c r="S12" t="n">
-        <v>-11.6838</v>
+        <v>0.5044</v>
       </c>
       <c r="T12" t="n">
-        <v>-8.392300000000001</v>
+        <v>0.3175</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.292</v>
+        <v>0.1871</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.1194</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>18.8569</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-20.9759</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>25</v>
       </c>
       <c r="D13" t="n">
-        <v>-15.4518</v>
+        <v>-6.1012</v>
       </c>
       <c r="E13" t="n">
-        <v>-17.2429</v>
+        <v>-11.9714</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7909</v>
+        <v>5.8701</v>
       </c>
       <c r="G13" t="n">
         <v>-4.8371</v>
@@ -1468,13 +1468,13 @@
         <v>29.5593</v>
       </c>
       <c r="S13" t="n">
-        <v>-9.5572</v>
+        <v>-0.2066</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.6693</v>
+        <v>0.6020999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.8877</v>
+        <v>-0.8083999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-1.4542</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. LATORRE SEGURA</t>
+          <t>S. QUINTANA CALVENTE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>-16.4572</v>
+        <v>-12.5417</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.3069</v>
+        <v>-22.1398</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.1503</v>
+        <v>9.597900000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-13.8006</v>
+        <v>0.2891999999999983</v>
       </c>
       <c r="H14" t="n">
-        <v>-6.0179</v>
+        <v>5.4575</v>
       </c>
       <c r="I14" t="n">
-        <v>-7.7826</v>
+        <v>-5.168199999999998</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.9509</v>
+        <v>22.7538</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.1753</v>
+        <v>18.8295</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.7755</v>
+        <v>3.9245</v>
       </c>
       <c r="M14" t="n">
-        <v>-8.849599999999999</v>
+        <v>-22.4645</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.8425</v>
+        <v>-13.3722</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.007099999999999</v>
+        <v>-9.092700000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>4.364599999999999</v>
+        <v>-18.4496</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.5709</v>
+        <v>-63.4827</v>
       </c>
       <c r="R14" t="n">
-        <v>7.9357</v>
+        <v>45.0334</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3262</v>
+        <v>-3.2745</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1107</v>
+        <v>-3.7443</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2156</v>
+        <v>0.4695999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-5.6952</v>
+        <v>8.8931</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.6745</v>
+        <v>22.3337</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.0207</v>
+        <v>-13.4399</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. BERNADÍ VALLS</t>
+          <t>A. LATORRE SEGURA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D15" t="n">
-        <v>-17.2398</v>
+        <v>-13.9121</v>
       </c>
       <c r="E15" t="n">
-        <v>-19.9487</v>
+        <v>-8.322900000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7089</v>
+        <v>-5.589099999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>-34.4941</v>
+        <v>-13.8006</v>
       </c>
       <c r="H15" t="n">
-        <v>-37.3534</v>
+        <v>-6.0179</v>
       </c>
       <c r="I15" t="n">
-        <v>2.859399999999999</v>
+        <v>-7.7826</v>
       </c>
       <c r="J15" t="n">
-        <v>-14.2189</v>
+        <v>-4.9509</v>
       </c>
       <c r="K15" t="n">
-        <v>-22.4596</v>
+        <v>-2.1753</v>
       </c>
       <c r="L15" t="n">
-        <v>8.2408</v>
+        <v>-2.7755</v>
       </c>
       <c r="M15" t="n">
-        <v>-20.2753</v>
+        <v>-8.849599999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-14.8936</v>
+        <v>-3.8425</v>
       </c>
       <c r="O15" t="n">
-        <v>-5.381699999999999</v>
+        <v>-5.007099999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>10.7127</v>
+        <v>4.364599999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>-15.6722</v>
+        <v>-3.5709</v>
       </c>
       <c r="R15" t="n">
-        <v>26.3853</v>
+        <v>7.9357</v>
       </c>
       <c r="S15" t="n">
-        <v>8.4383</v>
+        <v>1.2188</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1151999999999998</v>
+        <v>0.8731</v>
       </c>
       <c r="U15" t="n">
-        <v>8.323500000000001</v>
+        <v>0.3455</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.8968</v>
+        <v>-5.6952</v>
       </c>
       <c r="W15" t="n">
-        <v>9.827299999999999</v>
+        <v>-0.6745</v>
       </c>
       <c r="X15" t="n">
-        <v>-11.7241</v>
+        <v>-5.0207</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. QUINTANA CALVENTE</t>
+          <t>M. BERNADÍ VALLS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D16" t="n">
-        <v>-29.63</v>
+        <v>-21.1183</v>
       </c>
       <c r="E16" t="n">
-        <v>-35.1936</v>
+        <v>-21.4284</v>
       </c>
       <c r="F16" t="n">
-        <v>5.563800000000001</v>
+        <v>0.3099000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2891999999999983</v>
+        <v>-34.4941</v>
       </c>
       <c r="H16" t="n">
-        <v>5.4575</v>
+        <v>-37.3534</v>
       </c>
       <c r="I16" t="n">
-        <v>-5.168199999999998</v>
+        <v>2.859399999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>22.7538</v>
+        <v>-14.2189</v>
       </c>
       <c r="K16" t="n">
-        <v>18.8295</v>
+        <v>-22.4596</v>
       </c>
       <c r="L16" t="n">
-        <v>3.9245</v>
+        <v>8.2408</v>
       </c>
       <c r="M16" t="n">
-        <v>-22.4645</v>
+        <v>-20.2753</v>
       </c>
       <c r="N16" t="n">
-        <v>-13.3722</v>
+        <v>-14.8936</v>
       </c>
       <c r="O16" t="n">
-        <v>-9.092700000000001</v>
+        <v>-5.381699999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>-18.4496</v>
+        <v>10.7127</v>
       </c>
       <c r="Q16" t="n">
-        <v>-63.4827</v>
+        <v>-15.6722</v>
       </c>
       <c r="R16" t="n">
-        <v>45.0334</v>
+        <v>26.3853</v>
       </c>
       <c r="S16" t="n">
-        <v>-20.3627</v>
+        <v>4.5598</v>
       </c>
       <c r="T16" t="n">
-        <v>-16.7982</v>
+        <v>-1.3645</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.5646</v>
+        <v>5.9244</v>
       </c>
       <c r="V16" t="n">
-        <v>8.8931</v>
+        <v>-1.8968</v>
       </c>
       <c r="W16" t="n">
-        <v>22.3337</v>
+        <v>9.827299999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>-13.4399</v>
+        <v>-11.7241</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>17.3914</v>
+        <v>38.36259999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>-17.88589999999998</v>
+        <v>-9.157900000000005</v>
       </c>
       <c r="F17" t="n">
-        <v>35.27719999999999</v>
+        <v>47.52070000000001</v>
       </c>
       <c r="G17" t="n">
         <v>-42.0019</v>
@@ -1759,7 +1759,7 @@
         <v>113.7887</v>
       </c>
       <c r="L17" t="n">
-        <v>86.94489999999999</v>
+        <v>86.94490000000002</v>
       </c>
       <c r="M17" t="n">
         <v>-242.7369</v>
@@ -1780,16 +1780,16 @@
         <v>424.5433</v>
       </c>
       <c r="S17" t="n">
-        <v>12.47100000000001</v>
+        <v>33.443</v>
       </c>
       <c r="T17" t="n">
-        <v>4.103900000000003</v>
+        <v>12.8319</v>
       </c>
       <c r="U17" t="n">
-        <v>8.367299999999998</v>
+        <v>20.6114</v>
       </c>
       <c r="V17" t="n">
-        <v>-7.632899999999999</v>
+        <v>-7.6329</v>
       </c>
       <c r="W17" t="n">
         <v>147.2623</v>
